--- a/database/vocab.xlsx
+++ b/database/vocab.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\malek\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\kawkab\backend\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536DE665-917B-4F53-91DE-8B5EB362BF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D128B79-71C8-4AC1-9124-569F902FA171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2196" yWindow="2196" windowWidth="10956" windowHeight="9840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2998,10 +2998,10 @@
     <t>The car broke down on the highway.</t>
   </si>
   <si>
-    <t>correct choice</t>
-  </si>
-  <si>
     <t>unit</t>
+  </si>
+  <si>
+    <t>answer</t>
   </si>
 </sst>
 </file>
@@ -3293,10 +3293,10 @@
         <v>192</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>992</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
